--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2094.62</v>
+        <v>2076.88</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2835.5</v>
+        <v>2811.48</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3946.48</v>
+        <v>3913.06</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2016.94</v>
+        <v>1999.86</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>795.47</v>
+        <v>787.14</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>807.96</v>
+        <v>803.55</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1096.78</v>
+        <v>1090.79</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11530.9</v>
+        <v>11467.75</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3558.69</v>
+        <v>3570.4</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2033.57</v>
+        <v>2047.66</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4945.92</v>
+        <v>4980.18</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1088.69</v>
+        <v>1096.54</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1176.14</v>
+        <v>1182.21</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5019.42</v>
+        <v>4954.54</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15417.9</v>
+        <v>15218.61</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1018.98</v>
+        <v>1015.33</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>945.12</v>
+        <v>941.73</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>852.85</v>
+        <v>842.98</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6624.37</v>
+        <v>6547.7</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>775.27</v>
+        <v>766.29</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>775.83</v>
+        <v>766.85</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4179.32</v>
+        <v>4173.46</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2071.81</v>
+        <v>2018.91</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>927.13</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1521.7</v>
+        <v>1486.1</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1745.17</v>
+        <v>1704.34</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>933.46</v>
+        <v>932.8200000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>927.13</v>
+        <v>926.5</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5618.07</v>
+        <v>5598.79</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1527.08</v>
+        <v>1537.09</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1382.89</v>
+        <v>1391.95</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3455.17</v>
+        <v>3507.77</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2836.19</v>
+        <v>2847.98</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1058.14</v>
+        <v>1062.54</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1451.78</v>
+        <v>1443.87</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2963.77</v>
+        <v>2979.11</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1347.36</v>
+        <v>1354.34</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1533.32</v>
+        <v>1513.58</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21364.42</v>
+        <v>21089.37</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2806.8</v>
+        <v>2770.67</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2169.72</v>
+        <v>2154.4</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8707.379999999999</v>
+        <v>8645.93</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1632.95</v>
+        <v>1662.56</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>878.87</v>
+        <v>894.8099999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1328.51</v>
+        <v>1322.57</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3629.27</v>
+        <v>3613.64</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2962.75</v>
+        <v>2919.89</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>37520.02</v>
+        <v>36712.77</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5651.68</v>
+        <v>5530.09</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>900.71</v>
+        <v>881.33</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1481.99</v>
+        <v>1434.73</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2240.68</v>
+        <v>2196.49</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2053.74</v>
+        <v>1999.66</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10053.78</v>
+        <v>9871.459999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>14578.68</v>
+        <v>14314.3</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3145.63</v>
+        <v>3158.7</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1003.63</v>
+        <v>1012.14</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>889.3</v>
+        <v>896.85</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1361.45</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7741.64</v>
+        <v>7836.92</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>795.2</v>
+        <v>814.77</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8788.24</v>
+        <v>8844.450000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1976.17</v>
+        <v>1988.81</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>935.5700000000001</v>
+        <v>937.51</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10326.97</v>
+        <v>10442.46</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8455.959999999999</v>
+        <v>8550.530000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3923.28</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11812</v>
+        <v>11901.47</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4937.58</v>
+        <v>4956.28</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1235.45</v>
+        <v>1232.33</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1650.98</v>
+        <v>1646.81</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1610.61</v>
+        <v>1622.61</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6257.97</v>
+        <v>6242.52</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>828.5599999999999</v>
+        <v>826.52</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1395.87</v>
+        <v>1392.42</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1007.05</v>
+        <v>1024.08</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>929.88</v>
+        <v>939.34</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1600.36</v>
+        <v>1616.64</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>11158.32</v>
+        <v>11271.79</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>929.88</v>
+        <v>934.1</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>843.74</v>
+        <v>859.78</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10432.77</v>
+        <v>10504.8</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1289.47</v>
+        <v>1286.06</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>15700.05</v>
+        <v>15658.53</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>841.02</v>
+        <v>849</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>902.33</v>
+        <v>905.85</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1954.74</v>
+        <v>1962.37</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15234.84</v>
+        <v>15294.15</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1401.97</v>
+        <v>1405.18</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>15234.84</v>
+        <v>14990.57</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>10123.63</v>
+        <v>10067.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>720-498-CM25</t>
+          <t>1075963-18346-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2076.88</v>
+        <v>1674.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2366-4361-CM25</t>
+          <t>1075963-51947-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2811.48</v>
+        <v>1999.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2366-4363-CM25</t>
+          <t>720-498-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3913.06</v>
+        <v>2076.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1075963-51947-CM25</t>
+          <t>2366-4361-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1999.86</v>
+        <v>2811.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5951-5594-CM25</t>
+          <t>2366-4363-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>787.14</v>
+        <v>3913.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>707409-130-CM25</t>
+          <t>5951-5594-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>803.55</v>
+        <v>787.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1075963-52111-CM25</t>
+          <t>707409-130-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1090.79</v>
+        <v>803.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2366-4382-CM25</t>
+          <t>1075963-52111-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11467.75</v>
+        <v>1090.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5951-5607-CM25</t>
+          <t>2366-4382-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3570.4</v>
+        <v>11467.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2366-4323-CM25</t>
+          <t>5951-5607-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2047.66</v>
+        <v>3570.4</v>
       </c>
     </row>
     <row r="12">
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1075963-55691-CM25</t>
+          <t>2366-4323-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1096.54</v>
+        <v>2047.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1075963-56313-CM25</t>
+          <t>1075963-55691-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1182.21</v>
+        <v>1096.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2366-4436-CM25</t>
+          <t>1075963-56313-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4954.54</v>
+        <v>1182.21</v>
       </c>
     </row>
     <row r="16">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1075963-56306-CM25</t>
+          <t>2366-4436-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1015.33</v>
+        <v>4954.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1075963-56342-CM25</t>
+          <t>1075963-56306-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>941.73</v>
+        <v>1015.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1075963-60221-CM25</t>
+          <t>1075963-56342-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>842.98</v>
+        <v>941.73</v>
       </c>
     </row>
     <row r="20">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1075963-60311-CM25</t>
+          <t>1075963-60221-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4173.46</v>
+        <v>842.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1075963-64659-CM25</t>
+          <t>1075963-60311-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2018.91</v>
+        <v>4173.46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1075963-61156-CM25</t>
+          <t>1075963-64659-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>2018.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1075963-61157-CM25</t>
+          <t>1075963-61156-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1486.1</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1075963-61158-CM25</t>
+          <t>1075963-61157-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1704.34</v>
+        <v>1486.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1075963-838-CM26</t>
+          <t>1075963-61158-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>932.8200000000001</v>
+        <v>1704.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1075963-839-CM26</t>
+          <t>1075963-838-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>926.5</v>
+        <v>932.8200000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1075963-837-CM26</t>
+          <t>1075963-839-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5598.79</v>
+        <v>926.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1075963-1328-CM26</t>
+          <t>1075963-837-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1537.09</v>
+        <v>5598.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1075963-1329-CM26</t>
+          <t>1075963-1328-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1391.95</v>
+        <v>1537.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1075963-1389-CM26</t>
+          <t>1075963-1329-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3507.77</v>
+        <v>1391.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1075963-1511-CM26</t>
+          <t>1075963-1389-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2847.98</v>
+        <v>3507.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1075963-1491-CM26</t>
+          <t>1075963-1511-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1062.54</v>
+        <v>2847.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1075963-2540-CM26</t>
+          <t>1075963-1491-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1443.87</v>
+        <v>1062.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2366-101-CM26</t>
+          <t>1075963-2540-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2979.11</v>
+        <v>1443.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2366-102-CM26</t>
+          <t>2366-101-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1354.34</v>
+        <v>2979.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2366-91-CM26</t>
+          <t>2366-102-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1513.58</v>
+        <v>1354.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2366-93-CM26</t>
+          <t>2366-91-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>VAMPRODEN SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.962.948-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21089.37</v>
+        <v>1513.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2366-94-CM26</t>
+          <t>2366-93-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2770.67</v>
+        <v>21089.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2366-62-CM26</t>
+          <t>2366-94-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2154.4</v>
+        <v>2770.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2366-63-CM26</t>
+          <t>2366-62-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8645.93</v>
+        <v>2154.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3390-78-CM26</t>
+          <t>2366-63-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1662.56</v>
+        <v>8645.93</v>
       </c>
     </row>
     <row r="45">
@@ -3198,7 +3198,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1075963-3630-CM26</t>
+          <t>3390-78-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1322.57</v>
+        <v>1662.56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1075963-4169-CM26</t>
+          <t>1075963-3630-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3613.64</v>
+        <v>1322.57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3348-38-CM26</t>
+          <t>1075963-4169-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.116.604-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2919.89</v>
+        <v>3613.64</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2366-151-CM26</t>
+          <t>3348-38-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>36712.77</v>
+        <v>2919.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2366-152-CM26</t>
+          <t>2366-151-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5530.09</v>
+        <v>36712.77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1075963-4123-CM26</t>
+          <t>2366-152-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>881.33</v>
+        <v>5530.09</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075963-4373-CM26</t>
+          <t>1075963-4123-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1434.73</v>
+        <v>881.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1075963-4521-CM26</t>
+          <t>1075963-4373-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2196.49</v>
+        <v>1434.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1075963-4615-CM26</t>
+          <t>1075963-4521-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1999.66</v>
+        <v>2196.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1075963-4435-CM26</t>
+          <t>1075963-4615-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9871.459999999999</v>
+        <v>1999.66</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1075963-4644-CM26</t>
+          <t>1075963-4435-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>14314.3</v>
+        <v>9871.459999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3348-45-CM26</t>
+          <t>1075963-4644-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3158.7</v>
+        <v>14314.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1075963-4918-CM26</t>
+          <t>3348-45-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1012.14</v>
+        <v>3158.7</v>
       </c>
     </row>
     <row r="59">
@@ -4113,7 +4113,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>806208-22-CM26</t>
+          <t>1075963-4918-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,22 +4128,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7836.92</v>
+        <v>1012.14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1075963-5139-CM26</t>
+          <t>806208-22-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,22 +4189,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>814.77</v>
+        <v>7836.92</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1347870-9-CM26</t>
+          <t>1075963-5139-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8844.450000000001</v>
+        <v>814.77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1347870-12-CM26</t>
+          <t>1347870-9-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1988.81</v>
+        <v>8844.450000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1075963-5718-CM26</t>
+          <t>1347870-12-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>937.51</v>
+        <v>1988.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1347870-29-CM26</t>
+          <t>1075963-5718-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10442.46</v>
+        <v>937.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1347870-30-CM26</t>
+          <t>1347870-29-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>VAMPRODEN SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>76.962.948-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8550.530000000001</v>
+        <v>10442.46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2366-267-CM26</t>
+          <t>1347870-30-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3953</v>
+        <v>8550.530000000001</v>
       </c>
     </row>
     <row r="69">
@@ -4662,7 +4662,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>635-523-CM26</t>
+          <t>2366-267-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Clan Dent</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.371.920-9</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4956.28</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2366-253-CM26</t>
+          <t>635-523-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>Clan Dent</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.371.920-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1232.33</v>
+        <v>4956.28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2366-259-CM26</t>
+          <t>2366-253-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1646.81</v>
+        <v>1232.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1075963-6511-CM26</t>
+          <t>2366-259-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1622.61</v>
+        <v>1646.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2366-306-CM26</t>
+          <t>1075963-6511-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>PARACARE S.P.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.102.620-6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6242.52</v>
+        <v>1622.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1075963-6591-CM26</t>
+          <t>2366-306-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4987,17 +4987,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>826.52</v>
+        <v>6242.52</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1075963-6633-CM26</t>
+          <t>1075963-6591-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1392.42</v>
+        <v>826.52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1075963-7428-CM26</t>
+          <t>1075963-6633-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1024.08</v>
+        <v>1392.42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1075963-7189-CM26</t>
+          <t>1075963-7428-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>939.34</v>
+        <v>1024.08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1075963-7443-CM26</t>
+          <t>1075963-7447-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1616.64</v>
+        <v>11271.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1075963-7447-CM26</t>
+          <t>1075963-7443-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>PARACARE S.P.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>77.102.620-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>11271.79</v>
+        <v>1616.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1075963-7767-CM26</t>
+          <t>1075963-7189-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>934.1</v>
+        <v>939.34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5702-436-CM26</t>
+          <t>1075963-7767-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>859.78</v>
+        <v>934.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1075963-8044-CM26</t>
+          <t>5702-436-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10504.8</v>
+        <v>859.78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1075963-8042-CM26</t>
+          <t>1075963-8044-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1286.06</v>
+        <v>10504.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1075963-8151-CM26</t>
+          <t>1075963-8042-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>15658.53</v>
+        <v>1286.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>720-170-CM26</t>
+          <t>1075963-8151-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>849</v>
+        <v>15658.53</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1075963-8534-CM26</t>
+          <t>720-170-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>905.85</v>
+        <v>849</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1075963-8636-CM26</t>
+          <t>1075963-8534-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1962.37</v>
+        <v>905.85</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1075963-8986-CM26</t>
+          <t>1075963-8636-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15294.15</v>
+        <v>1962.37</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1075963-9112-CM26</t>
+          <t>1075963-8986-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1405.18</v>
+        <v>15294.15</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1075963-9701-CM26</t>
+          <t>1075963-9112-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>14990.57</v>
+        <v>1405.18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1075963-9808-CM26</t>
+          <t>1075963-9701-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,6 +6059,67 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
+        <v>14990.57</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1075963-9808-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
         <v>10067.51</v>
       </c>
     </row>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1075963-18346-CM25</t>
+          <t>1075963-310-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1674.14</v>
+        <v>800.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1075963-51947-CM25</t>
+          <t>1075963-337-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1999.86</v>
+        <v>2993.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>720-498-CM25</t>
+          <t>1075963-476-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2076.88</v>
+        <v>1168.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2366-4361-CM25</t>
+          <t>1075963-921-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2811.48</v>
+        <v>3780.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2366-4363-CM25</t>
+          <t>1075963-922-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3913.06</v>
+        <v>2336.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5951-5594-CM25</t>
+          <t>1075963-2044-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>787.14</v>
+        <v>8077.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>707409-130-CM25</t>
+          <t>1075963-2376-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>803.55</v>
+        <v>816.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1075963-52111-CM25</t>
+          <t>1075963-6519-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1090.79</v>
+        <v>1369.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2366-4382-CM25</t>
+          <t>1075963-7603-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11467.75</v>
+        <v>2558.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5951-5607-CM25</t>
+          <t>1075963-7390-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3570.4</v>
+        <v>5824.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2366-4322-CM25</t>
+          <t>1075963-15285-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>Dolphin Medical</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>77.783.690-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4980.18</v>
+        <v>1135.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2366-4323-CM25</t>
+          <t>1075963-15286-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2047.66</v>
+        <v>1257.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1075963-55691-CM25</t>
+          <t>1075963-14958-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1096.54</v>
+        <v>1455.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1075963-56313-CM25</t>
+          <t>1075963-15830-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Dolphin Medical</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.783.690-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1182.21</v>
+        <v>7029.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2366-4437-CM25</t>
+          <t>1075963-18346-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15218.61</v>
+        <v>1674.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2366-4436-CM25</t>
+          <t>720-138-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4954.54</v>
+        <v>844.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1075963-56306-CM25</t>
+          <t>1075963-18854-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1015.33</v>
+        <v>4352.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1075963-56342-CM25</t>
+          <t>1075963-18881-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>941.73</v>
+        <v>4672.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2366-4426-CM25</t>
+          <t>5512-123-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6547.7</v>
+        <v>3821.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1075963-60181-CM25</t>
+          <t>5951-52-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>766.29</v>
+        <v>5238.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1075963-60182-CM25</t>
+          <t>1075963-19542-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>766.85</v>
+        <v>871.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1075963-60221-CM25</t>
+          <t>720-229-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>842.98</v>
+        <v>734.6900000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1075963-60311-CM25</t>
+          <t>1075963-20064-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4173.46</v>
+        <v>4107.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1075963-64659-CM25</t>
+          <t>2366-3878-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2018.91</v>
+        <v>1661.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1075963-61156-CM25</t>
+          <t>1075963-20525-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>1457.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1075963-61157-CM25</t>
+          <t>1075963-20871-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1486.1</v>
+        <v>849.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1075963-61158-CM25</t>
+          <t>806208-34-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1704.34</v>
+        <v>3025.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1075963-838-CM26</t>
+          <t>1075963-21036-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>932.8200000000001</v>
+        <v>907.8099999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1075963-839-CM26</t>
+          <t>2366-3987-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>926.5</v>
+        <v>5879.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1075963-837-CM26</t>
+          <t>1075963-21460-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5598.79</v>
+        <v>4748.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1075963-1328-CM26</t>
+          <t>2366-4046-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1537.09</v>
+        <v>3752.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1075963-1329-CM26</t>
+          <t>2366-4045-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1391.95</v>
+        <v>864.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1075963-1389-CM26</t>
+          <t>1075963-22048-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3507.77</v>
+        <v>1921.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1075963-1511-CM26</t>
+          <t>2366-3995-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2847.98</v>
+        <v>2910.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1075963-1491-CM26</t>
+          <t>1075963-22298-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,17 +2598,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1062.54</v>
+        <v>1193.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1075963-2540-CM26</t>
+          <t>1075963-19546-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1443.87</v>
+        <v>2554.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2366-101-CM26</t>
+          <t>1075963-22579-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2979.11</v>
+        <v>944.58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2366-102-CM26</t>
+          <t>1075963-22606-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1354.34</v>
+        <v>1382.54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2366-91-CM26</t>
+          <t>1347870-90-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1513.58</v>
+        <v>13309.29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2366-93-CM26</t>
+          <t>1347870-89-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21089.37</v>
+        <v>1000.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2366-94-CM26</t>
+          <t>1075963-23046-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2770.67</v>
+        <v>1408.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2366-62-CM26</t>
+          <t>720-365-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2154.4</v>
+        <v>3939.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2366-63-CM26</t>
+          <t>1075963-23905-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8645.93</v>
+        <v>1376.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1075963-3296-CM26</t>
+          <t>1075963-24130-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>894.8099999999999</v>
+        <v>1031.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3390-78-CM26</t>
+          <t>1075963-24327-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1662.56</v>
+        <v>1268.56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1075963-3630-CM26</t>
+          <t>2366-4131-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.012.551-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1322.57</v>
+        <v>14658.32</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1075963-4169-CM26</t>
+          <t>2366-4183-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3613.64</v>
+        <v>8538.790000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3348-38-CM26</t>
+          <t>837-493-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2919.89</v>
+        <v>8498.219999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2366-151-CM26</t>
+          <t>1075963-32548-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>36712.77</v>
+        <v>1439.98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2366-152-CM26</t>
+          <t>1075963-32724-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5530.09</v>
+        <v>7135.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075963-4123-CM26</t>
+          <t>1075963-37369-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>881.33</v>
+        <v>956.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1075963-4373-CM26</t>
+          <t>1075963-37301-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,17 +3635,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1434.73</v>
+        <v>1723.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1075963-4521-CM26</t>
+          <t>1075963-44285-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2196.49</v>
+        <v>1567.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1075963-4615-CM26</t>
+          <t>5951-156-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1999.66</v>
+        <v>740.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1075963-4435-CM26</t>
+          <t>2366-4271-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9871.459999999999</v>
+        <v>3994.68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1075963-4644-CM26</t>
+          <t>1075963-44052-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,17 +3879,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>14314.3</v>
+        <v>857.21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3348-45-CM26</t>
+          <t>5951-158-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3158.7</v>
+        <v>956.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1075963-4794-CM26</t>
+          <t>2366-4315-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>896.85</v>
+        <v>843.48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1075963-4877-CM26</t>
+          <t>2366-4347-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1373</v>
+        <v>9475.110000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1075963-4918-CM26</t>
+          <t>1075963-48938-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1012.14</v>
+        <v>1814.18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>806208-22-CM26</t>
+          <t>5951-174-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7836.92</v>
+        <v>995.1900000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1075963-5139-CM26</t>
+          <t>1075963-48922-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>814.77</v>
+        <v>2986.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1347870-9-CM26</t>
+          <t>2366-4356-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MEDICALTEK CHILE S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.696.000-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8844.450000000001</v>
+        <v>12047.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1347870-12-CM26</t>
+          <t>5951-195-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,27 +4367,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1988.81</v>
+        <v>3871.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1075963-5718-CM26</t>
+          <t>2366-4363-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>937.51</v>
+        <v>3913.06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1347870-29-CM26</t>
+          <t>720-498-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10442.46</v>
+        <v>2076.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1347870-30-CM26</t>
+          <t>1075963-51947-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8550.530000000001</v>
+        <v>1999.86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1075963-6344-CM26</t>
+          <t>2366-4361-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11901.47</v>
+        <v>2811.48</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2366-267-CM26</t>
+          <t>5951-5594-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3953</v>
+        <v>787.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>635-523-CM26</t>
+          <t>707409-130-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Clan Dent</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.371.920-9</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4956.28</v>
+        <v>803.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2366-253-CM26</t>
+          <t>1075963-52111-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1232.33</v>
+        <v>1090.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2366-259-CM26</t>
+          <t>2366-4382-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1646.81</v>
+        <v>11467.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1075963-6511-CM26</t>
+          <t>5951-5607-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,27 +4916,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1622.61</v>
+        <v>3570.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2366-306-CM26</t>
+          <t>2366-4322-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.910.467-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6242.52</v>
+        <v>4980.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1075963-6591-CM26</t>
+          <t>2366-4323-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>826.52</v>
+        <v>2047.66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1075963-6633-CM26</t>
+          <t>1075963-55691-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1392.42</v>
+        <v>1096.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1075963-7428-CM26</t>
+          <t>1075963-56313-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1024.08</v>
+        <v>1182.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1075963-7447-CM26</t>
+          <t>2366-4437-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>11271.79</v>
+        <v>15218.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1075963-7443-CM26</t>
+          <t>2366-4436-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1616.64</v>
+        <v>4954.54</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1075963-7189-CM26</t>
+          <t>1075963-56306-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>939.34</v>
+        <v>1015.33</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1075963-7767-CM26</t>
+          <t>1075963-56342-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>934.1</v>
+        <v>941.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5702-436-CM26</t>
+          <t>1075963-60221-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>859.78</v>
+        <v>842.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1075963-8044-CM26</t>
+          <t>2366-4426-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>10504.8</v>
+        <v>6547.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1075963-8042-CM26</t>
+          <t>1075963-60181-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1286.06</v>
+        <v>766.29</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1075963-8151-CM26</t>
+          <t>1075963-60182-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>15658.53</v>
+        <v>766.85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>720-170-CM26</t>
+          <t>1075963-60311-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>849</v>
+        <v>4173.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1075963-8534-CM26</t>
+          <t>1075963-64659-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>905.85</v>
+        <v>2018.91</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1075963-8636-CM26</t>
+          <t>1075963-61156-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1962.37</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1075963-8986-CM26</t>
+          <t>1075963-61157-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>15294.15</v>
+        <v>1486.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1075963-9112-CM26</t>
+          <t>1075963-61158-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1405.18</v>
+        <v>1704.34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1075963-9701-CM26</t>
+          <t>1075963-838-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>14990.57</v>
+        <v>932.8200000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1075963-9808-CM26</t>
+          <t>1075963-839-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,7 +6120,4582 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
+        <v>926.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1075963-837-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>5598.79</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1075963-1329-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1391.95</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1075963-1328-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>1537.09</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1075963-1389-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>3507.77</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1075963-1491-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>1062.54</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1075963-1511-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>2847.98</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1075963-2540-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>COMERCIAL LIMAX SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.719.400-5</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>1443.87</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2366-101-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>2979.11</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2366-102-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>1354.34</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2366-91-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>VAMPRODEN SPA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>76.962.948-3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>1513.58</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2366-93-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>21089.37</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2366-94-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Dipromed S.A.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>86.397.000-8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>2770.67</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2366-62-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>2154.4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2366-63-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>8645.93</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1075963-3296-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>894.8099999999999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3390-78-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>1662.56</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1075963-3630-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>1322.57</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1075963-4169-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>3613.64</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3348-38-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>2919.89</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2366-151-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>36712.77</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2366-152-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>5530.09</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1075963-4123-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>881.33</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1075963-4373-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1434.73</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1075963-4521-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>2196.49</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1075963-4615-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>1999.66</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1075963-4435-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>TECHDOMIPAR SPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.500.331-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>9871.459999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1075963-4644-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>14314.3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3348-45-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>3158.7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1075963-4877-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1075963-4918-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>1012.14</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1075963-4794-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>896.85</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>806208-22-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>7836.92</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1075963-5139-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>814.77</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1347870-9-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>8844.450000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1347870-12-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Jocelyn</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.226.228-2</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>1988.81</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1075963-5718-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>937.51</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1347870-29-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>VAMPRODEN SPA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>76.962.948-3</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>10442.46</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1347870-30-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Dipromed S.A.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>86.397.000-8</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>8550.530000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2366-267-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1075963-6344-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>11901.47</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>635-523-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Clan Dent</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>77.371.920-9</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>4956.28</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2366-253-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>1232.33</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2366-259-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>1646.81</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1075963-6511-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>PARACARE S.P.A.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>77.102.620-6</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>1622.61</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1075963-6633-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>1392.42</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1075963-6591-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>826.52</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2366-306-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>6242.52</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1075963-7428-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>1024.08</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1075963-7189-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>939.34</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1075963-7443-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>PARACARE S.P.A.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>77.102.620-6</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>1616.64</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1075963-7447-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>GLOMAX S.A.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>76.817.867-4</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>11271.79</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1075963-7767-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>934.1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>5702-436-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>859.78</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1075963-8044-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>10504.8</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1075963-8042-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>1286.06</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1075963-8151-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>GLOMAX S.A.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>76.817.867-4</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>15658.53</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>720-170-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1075963-8534-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>905.85</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1075963-8636-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>1962.37</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1075963-8986-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>GLOMAX S.A.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>76.817.867-4</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>15294.15</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1075963-9112-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Comercial LBF Limitada</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>1405.18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1075963-9701-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>GLOMAX S.A.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.817.867-4</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>14990.57</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1075963-9808-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
         <v>10067.51</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1075963-9572-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>1206.41</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1075963-9581-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>962.85</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1075963-10043-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>2786.52</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2366-468-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>EXXIMMED 2000 SPA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>78.060.400-k</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>13260.76</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1075963-10361-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>TECHDOMIPAR SPA</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>76.500.331-8</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>3686.81</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1075963-10630-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>2095.4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1075963-10538-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>800.11</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1075963-10905-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>COMERCIAL LBF LIMITADA</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>1418.29</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1075963-11027-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>1430.85</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1075963-11261-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>4979.39</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1075963-11254-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>10186.22</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1075963-11375-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>3938.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1075963-18346-CM25</t>
+          <t>720-138-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1674.14</v>
+        <v>844.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>720-138-CM25</t>
+          <t>1075963-18346-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>844.96</v>
+        <v>1674.14</v>
       </c>
     </row>
     <row r="18">
@@ -2344,7 +2344,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2366-4046-CM25</t>
+          <t>2366-4045-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3752.62</v>
+        <v>864.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2366-4045-CM25</t>
+          <t>2366-4046-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>864.15</v>
+        <v>3752.62</v>
       </c>
     </row>
     <row r="34">
@@ -4418,7 +4418,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2366-4363-CM25</t>
+          <t>720-498-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3913.06</v>
+        <v>2076.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>720-498-CM25</t>
+          <t>2366-4361-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2076.88</v>
+        <v>2811.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1075963-51947-CM25</t>
+          <t>2366-4363-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1999.86</v>
+        <v>3913.06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2366-4361-CM25</t>
+          <t>1075963-51947-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2811.48</v>
+        <v>1999.86</v>
       </c>
     </row>
     <row r="70">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2366-4437-CM25</t>
+          <t>837-729-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOTECNO MEDICAL SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.758.693-0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>15218.61</v>
+        <v>3811.37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2366-4436-CM25</t>
+          <t>837-730-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4954.54</v>
+        <v>6209.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1075963-56306-CM25</t>
+          <t>2366-4436-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1015.33</v>
+        <v>4954.54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1075963-56342-CM25</t>
+          <t>2366-4437-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>941.73</v>
+        <v>15218.61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1075963-60221-CM25</t>
+          <t>837-745-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>842.98</v>
+        <v>765.4400000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2366-4426-CM25</t>
+          <t>1075963-56306-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6547.7</v>
+        <v>1015.33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1075963-60181-CM25</t>
+          <t>1075963-56342-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>766.29</v>
+        <v>941.73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1075963-60182-CM25</t>
+          <t>1075963-60181-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>766.85</v>
+        <v>766.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1075963-60311-CM25</t>
+          <t>1075963-60182-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4173.46</v>
+        <v>766.85</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1075963-64659-CM25</t>
+          <t>1075963-60221-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2018.91</v>
+        <v>842.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1075963-61156-CM25</t>
+          <t>2366-4426-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>6547.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1075963-61157-CM25</t>
+          <t>1075963-60311-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1486.1</v>
+        <v>4173.46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1075963-61158-CM25</t>
+          <t>1075963-64659-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1704.34</v>
+        <v>2018.91</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1075963-838-CM26</t>
+          <t>1075963-61156-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>932.8200000000001</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1075963-839-CM26</t>
+          <t>1075963-61157-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>926.5</v>
+        <v>1486.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1075963-837-CM26</t>
+          <t>1075963-61158-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5598.79</v>
+        <v>1704.34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1075963-1329-CM26</t>
+          <t>1075963-838-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1391.95</v>
+        <v>932.8200000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1075963-1328-CM26</t>
+          <t>1075963-839-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1537.09</v>
+        <v>926.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1075963-1389-CM26</t>
+          <t>1075963-837-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3507.77</v>
+        <v>5598.79</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1075963-1491-CM26</t>
+          <t>1075963-1328-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1062.54</v>
+        <v>1537.09</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1075963-1511-CM26</t>
+          <t>1075963-1329-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2847.98</v>
+        <v>1391.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1075963-2540-CM26</t>
+          <t>1075963-1389-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1443.87</v>
+        <v>3507.77</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2366-101-CM26</t>
+          <t>1075963-1511-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2979.11</v>
+        <v>2847.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2366-102-CM26</t>
+          <t>1075963-1491-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1354.34</v>
+        <v>1062.54</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2366-91-CM26</t>
+          <t>1075963-2540-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1513.58</v>
+        <v>1443.87</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2366-93-CM26</t>
+          <t>2366-101-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>21089.37</v>
+        <v>2979.11</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2366-94-CM26</t>
+          <t>2366-102-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2770.67</v>
+        <v>1354.34</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2366-62-CM26</t>
+          <t>2366-91-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>VAMPRODEN SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.962.948-3</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2154.4</v>
+        <v>1513.58</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2366-63-CM26</t>
+          <t>2366-93-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8645.93</v>
+        <v>21089.37</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1075963-3296-CM26</t>
+          <t>2366-94-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>894.8099999999999</v>
+        <v>2770.67</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3390-78-CM26</t>
+          <t>2366-62-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1662.56</v>
+        <v>2154.4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1075963-3630-CM26</t>
+          <t>2366-63-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1322.57</v>
+        <v>8645.93</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1075963-4169-CM26</t>
+          <t>1075963-3296-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3613.64</v>
+        <v>894.8099999999999</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3348-38-CM26</t>
+          <t>3390-78-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2919.89</v>
+        <v>1662.56</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2366-151-CM26</t>
+          <t>1075963-3630-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>36712.77</v>
+        <v>1322.57</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2366-152-CM26</t>
+          <t>1075963-4169-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.116.604-2</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5530.09</v>
+        <v>3613.64</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1075963-4123-CM26</t>
+          <t>3348-38-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>881.33</v>
+        <v>2919.89</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1075963-4373-CM26</t>
+          <t>2366-151-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7478,27 +7478,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1434.73</v>
+        <v>36712.77</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1075963-4521-CM26</t>
+          <t>2366-152-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2196.49</v>
+        <v>5530.09</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1075963-4615-CM26</t>
+          <t>1075963-4123-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1999.66</v>
+        <v>881.33</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1075963-4435-CM26</t>
+          <t>1075963-4373-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>9871.459999999999</v>
+        <v>1434.73</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1075963-4644-CM26</t>
+          <t>1075963-4521-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>14314.3</v>
+        <v>2196.49</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3348-45-CM26</t>
+          <t>1075963-4615-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3158.7</v>
+        <v>1999.66</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1075963-4877-CM26</t>
+          <t>1075963-4435-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1373</v>
+        <v>9871.459999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1075963-4918-CM26</t>
+          <t>1075963-4644-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1012.14</v>
+        <v>14314.3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1075963-4794-CM26</t>
+          <t>3348-45-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>896.85</v>
+        <v>3158.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>806208-22-CM26</t>
+          <t>1075963-4794-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,22 +8032,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7836.92</v>
+        <v>896.85</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1075963-5139-CM26</t>
+          <t>1075963-4877-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>814.77</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1347870-9-CM26</t>
+          <t>1075963-4918-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>8844.450000000001</v>
+        <v>1012.14</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1347870-12-CM26</t>
+          <t>806208-22-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1988.81</v>
+        <v>7836.92</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1075963-5718-CM26</t>
+          <t>1075963-5139-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>937.51</v>
+        <v>814.77</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1347870-29-CM26</t>
+          <t>1347870-9-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8332,17 +8332,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10442.46</v>
+        <v>8844.450000000001</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1347870-30-CM26</t>
+          <t>1347870-12-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>8550.530000000001</v>
+        <v>1988.81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2366-267-CM26</t>
+          <t>1075963-5718-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3953</v>
+        <v>937.51</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1075963-6344-CM26</t>
+          <t>1347870-29-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>VAMPRODEN SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.962.948-3</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>11901.47</v>
+        <v>10442.46</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>635-523-CM26</t>
+          <t>1347870-30-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Clan Dent</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.371.920-9</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4956.28</v>
+        <v>8550.530000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2366-253-CM26</t>
+          <t>1075963-6344-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1232.33</v>
+        <v>11901.47</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2366-259-CM26</t>
+          <t>2366-267-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1646.81</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1075963-6511-CM26</t>
+          <t>635-523-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>Clan Dent</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>77.371.920-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1622.61</v>
+        <v>4956.28</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1075963-6633-CM26</t>
+          <t>2366-253-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,22 +8825,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1392.42</v>
+        <v>1232.33</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1075963-6591-CM26</t>
+          <t>2366-259-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,22 +8886,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>826.52</v>
+        <v>1646.81</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2366-306-CM26</t>
+          <t>837-271-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>6242.52</v>
+        <v>2194.81</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1075963-7428-CM26</t>
+          <t>1075963-6511-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>PARACARE S.P.A.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.102.620-6</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1024.08</v>
+        <v>1622.61</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1075963-7189-CM26</t>
+          <t>2366-306-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>939.34</v>
+        <v>6242.52</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1075963-7443-CM26</t>
+          <t>1075963-6591-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1616.64</v>
+        <v>826.52</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1075963-7447-CM26</t>
+          <t>1075963-6633-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9186,17 +9186,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>11271.79</v>
+        <v>1392.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1075963-7767-CM26</t>
+          <t>1075963-7428-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>934.1</v>
+        <v>1024.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5702-436-CM26</t>
+          <t>1075963-7447-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>859.78</v>
+        <v>11271.79</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1075963-8044-CM26</t>
+          <t>1075963-7189-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>10504.8</v>
+        <v>939.34</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1075963-8042-CM26</t>
+          <t>1075963-7443-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>PARACARE S.P.A.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.102.620-6</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1286.06</v>
+        <v>1616.64</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1075963-8151-CM26</t>
+          <t>1075963-7767-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>15658.53</v>
+        <v>934.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>720-170-CM26</t>
+          <t>5702-436-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>849</v>
+        <v>859.78</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1075963-8534-CM26</t>
+          <t>1075963-8044-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>905.85</v>
+        <v>10504.8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1075963-8636-CM26</t>
+          <t>1075963-8151-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1962.37</v>
+        <v>15658.53</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1075963-8986-CM26</t>
+          <t>1075963-8042-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>15294.15</v>
+        <v>1286.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1075963-9112-CM26</t>
+          <t>720-170-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1405.18</v>
+        <v>849</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1075963-9701-CM26</t>
+          <t>1075963-8636-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>14990.57</v>
+        <v>1962.37</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1075963-9808-CM26</t>
+          <t>1075963-8534-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>10067.51</v>
+        <v>905.85</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1075963-9572-CM26</t>
+          <t>1075963-8986-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1206.41</v>
+        <v>15294.15</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1075963-9581-CM26</t>
+          <t>1075963-9112-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10040,17 +10040,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>962.85</v>
+        <v>1405.18</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1075963-10043-CM26</t>
+          <t>1075963-9701-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2786.52</v>
+        <v>14990.57</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2366-468-CM26</t>
+          <t>1075963-9808-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>13260.76</v>
+        <v>10067.51</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1075963-10361-CM26</t>
+          <t>1075963-9572-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>TECHDOMIPAR SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.500.331-8</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3686.81</v>
+        <v>1206.41</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1075963-10630-CM26</t>
+          <t>1075963-9581-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2095.4</v>
+        <v>962.85</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1075963-10538-CM26</t>
+          <t>1075963-10043-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>800.11</v>
+        <v>2786.52</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1075963-10905-CM26</t>
+          <t>2366-468-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1418.29</v>
+        <v>13260.76</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1075963-11027-CM26</t>
+          <t>1075963-10361-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECHDOMIPAR SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.500.331-8</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1430.85</v>
+        <v>3686.81</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1075963-11261-CM26</t>
+          <t>1075963-10630-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>4979.39</v>
+        <v>2095.4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1075963-11254-CM26</t>
+          <t>1075963-10538-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10186.22</v>
+        <v>800.11</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1075963-11375-CM26</t>
+          <t>1075963-10905-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,7 +10695,739 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
+        <v>1418.29</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1075963-11027-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>1430.85</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1075963-11261-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>4979.39</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1075963-11254-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>10186.22</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1075963-11375-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
         <v>3938.15</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1075963-11639-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>10087.01</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1075963-11898-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>15465.92</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1075963-12022-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1075963-11843-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>1102.03</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1075963-11982-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>755.53</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1075963-12366-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>1409.12</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1075963-12314-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>5417.38</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1075963-12451-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>COMERCIAL LBF LIMITADA</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>1516.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -623,7 +623,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1054,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1241,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1428,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1615,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1680,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1745,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1993,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2180,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2245,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2432,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2558,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2623,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2688,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2814,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2940,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3127,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3192,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3684,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3810,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3875,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3940,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4127,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4192,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4257,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4322,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4509,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4574,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4761,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4826,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4891,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5139,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5204,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5269,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5456,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5765,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6013,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6322,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6570,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6635,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6761,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6826,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7196,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7261,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7448,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7513,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7578,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8131,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8196,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8261,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8326,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8391,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8456,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8521,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8830,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8895,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8960,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9391,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9456,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9521,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9830,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9895,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10326,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10452,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10822,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10887,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10952,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11078,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11143,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11208,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11273,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11338,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11403,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11529,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11716,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1380,7 +1380,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>720-138-CM25</t>
+          <t>1075963-18346-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1420,32 +1420,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>844.96</v>
+        <v>1674.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1075963-18346-CM25</t>
+          <t>720-138-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1470,12 +1466,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1485,22 +1481,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1674.14</v>
+        <v>844.96</v>
       </c>
     </row>
     <row r="18">
@@ -3501,7 +3501,11 @@
           <t>84.609.600-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3636,7 +3640,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075963-37369-CM25</t>
+          <t>1075963-37301-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3676,32 +3680,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>956.12</v>
+        <v>1723.37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1075963-37301-CM25</t>
+          <t>1075963-37369-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3741,22 +3741,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1723.37</v>
+        <v>956.12</v>
       </c>
     </row>
     <row r="54">
@@ -3957,7 +3961,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1075963-44052-CM25</t>
+          <t>5951-158-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3977,17 +3981,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4012,13 +4016,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>857.21</v>
+        <v>956.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5951-158-CM25</t>
+          <t>1075963-44052-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4038,17 +4042,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4073,7 +4077,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>956.39</v>
+        <v>857.21</v>
       </c>
     </row>
     <row r="59">
@@ -5017,7 +5021,11 @@
           <t>84.609.600-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5656,7 +5664,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1075963-56306-CM25</t>
+          <t>1075963-56342-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5696,28 +5704,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1015.33</v>
+        <v>941.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1075963-56342-CM25</t>
+          <t>1075963-56306-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5757,32 +5769,28 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>941.73</v>
+        <v>1015.33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1075963-60181-CM25</t>
+          <t>2366-4426-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5807,12 +5815,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5822,28 +5830,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>766.29</v>
+        <v>6547.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1075963-60182-CM25</t>
+          <t>1075963-60181-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5883,12 +5895,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5898,13 +5910,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>766.85</v>
+        <v>766.29</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1075963-60221-CM25</t>
+          <t>1075963-60182-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5944,12 +5956,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5959,13 +5971,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>842.98</v>
+        <v>766.85</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2366-4426-CM25</t>
+          <t>1075963-60221-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5990,12 +6002,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6005,26 +6017,22 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6547.7</v>
+        <v>842.98</v>
       </c>
     </row>
     <row r="90">
@@ -6339,7 +6347,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1075963-838-CM26</t>
+          <t>1075963-839-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6379,12 +6387,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6394,13 +6402,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>932.8200000000001</v>
+        <v>926.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1075963-839-CM26</t>
+          <t>1075963-838-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6440,12 +6448,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6455,7 +6463,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>926.5</v>
+        <v>932.8200000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6522,7 +6530,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1075963-1328-CM26</t>
+          <t>1075963-1329-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6562,12 +6570,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6581,13 +6589,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1537.09</v>
+        <v>1391.95</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1075963-1329-CM26</t>
+          <t>1075963-1328-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6627,12 +6635,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6646,7 +6654,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1391.95</v>
+        <v>1537.09</v>
       </c>
     </row>
     <row r="100">
@@ -6713,7 +6721,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1075963-1511-CM26</t>
+          <t>1075963-1491-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6772,13 +6780,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2847.98</v>
+        <v>1062.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1075963-1491-CM26</t>
+          <t>1075963-1511-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6837,7 +6845,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1062.54</v>
+        <v>2847.98</v>
       </c>
     </row>
     <row r="103">
@@ -6904,7 +6912,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2366-101-CM26</t>
+          <t>2366-102-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6944,12 +6952,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6959,13 +6967,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2979.11</v>
+        <v>1354.34</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2366-102-CM26</t>
+          <t>2366-101-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7005,12 +7013,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -7020,13 +7028,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1354.34</v>
+        <v>2979.11</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2366-91-CM26</t>
+          <t>2366-94-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7066,22 +7074,26 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>86.397.000-8</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1513.58</v>
+        <v>2770.67</v>
       </c>
     </row>
     <row r="107">
@@ -7148,7 +7160,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2366-94-CM26</t>
+          <t>2366-91-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7188,32 +7200,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>VAMPRODEN SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.948-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2770.67</v>
+        <v>1513.58</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2366-62-CM26</t>
+          <t>2366-63-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7253,32 +7261,28 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2154.4</v>
+        <v>8645.93</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2366-63-CM26</t>
+          <t>2366-62-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7318,28 +7322,32 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8645.93</v>
+        <v>2154.4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1075963-3296-CM26</t>
+          <t>3390-78-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7364,12 +7372,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7379,28 +7387,32 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>894.8099999999999</v>
+        <v>1662.56</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3390-78-CM26</t>
+          <t>1075963-3296-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7425,12 +7437,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7440,26 +7452,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1662.56</v>
+        <v>894.8099999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7656,7 +7664,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2366-151-CM26</t>
+          <t>2366-152-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7696,12 +7704,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7711,13 +7719,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>36712.77</v>
+        <v>5530.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2366-152-CM26</t>
+          <t>1075963-4123-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7742,12 +7750,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7757,12 +7765,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7772,13 +7780,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5530.09</v>
+        <v>881.33</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1075963-4123-CM26</t>
+          <t>2366-151-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7803,12 +7811,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7818,12 +7826,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7833,7 +7841,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>881.33</v>
+        <v>36712.77</v>
       </c>
     </row>
     <row r="119">
@@ -8721,7 +8729,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1347870-29-CM26</t>
+          <t>1347870-30-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8761,28 +8769,32 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>VAMPRODEN SPA</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.962.948-3</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>86.397.000-8</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>10442.46</v>
+        <v>8550.530000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1347870-30-CM26</t>
+          <t>1347870-29-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8822,26 +8834,22 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>VAMPRODEN SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.948-3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>8550.530000000001</v>
+        <v>10442.46</v>
       </c>
     </row>
     <row r="135">
@@ -9038,7 +9046,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2366-253-CM26</t>
+          <t>2366-259-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9078,12 +9086,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -9093,13 +9101,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1232.33</v>
+        <v>1646.81</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2366-259-CM26</t>
+          <t>2366-253-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9139,12 +9147,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -9154,7 +9162,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1646.81</v>
+        <v>1232.33</v>
       </c>
     </row>
     <row r="140">
@@ -9282,7 +9290,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2366-306-CM26</t>
+          <t>1075963-6591-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9302,17 +9310,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9322,28 +9330,32 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6242.52</v>
+        <v>826.52</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1075963-6591-CM26</t>
+          <t>2366-306-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9363,17 +9375,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9383,26 +9395,22 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>826.52</v>
+        <v>6242.52</v>
       </c>
     </row>
     <row r="144">
@@ -9538,7 +9546,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1075963-7447-CM26</t>
+          <t>1075963-7443-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9578,12 +9586,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>PARACARE S.P.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>77.102.620-6</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9593,7 +9601,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11271.79</v>
+        <v>1616.64</v>
       </c>
     </row>
     <row r="147">
@@ -9660,7 +9668,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1075963-7443-CM26</t>
+          <t>1075963-7447-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9700,12 +9708,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>PARACARE S.P.A.</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.102.620-6</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9715,7 +9723,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1616.64</v>
+        <v>11271.79</v>
       </c>
     </row>
     <row r="149">
@@ -9912,7 +9920,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1075963-8151-CM26</t>
+          <t>1075963-8042-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9952,12 +9960,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9967,13 +9975,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>15658.53</v>
+        <v>1286.06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1075963-8042-CM26</t>
+          <t>1075963-8151-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10013,12 +10021,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -10028,7 +10036,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1286.06</v>
+        <v>15658.53</v>
       </c>
     </row>
     <row r="154">
@@ -10095,7 +10103,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1075963-8636-CM26</t>
+          <t>1075963-8534-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10135,12 +10143,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -10150,13 +10158,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1962.37</v>
+        <v>905.85</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1075963-8534-CM26</t>
+          <t>1075963-8636-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10196,12 +10204,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -10211,7 +10219,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>905.85</v>
+        <v>1962.37</v>
       </c>
     </row>
     <row r="157">
@@ -10530,7 +10538,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1075963-9581-CM26</t>
+          <t>1075963-10043-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10550,7 +10558,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10570,12 +10578,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10585,13 +10593,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>962.85</v>
+        <v>2786.52</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1075963-10043-CM26</t>
+          <t>1075963-9581-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10611,7 +10619,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10631,12 +10639,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10646,7 +10654,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2786.52</v>
+        <v>962.85</v>
       </c>
     </row>
     <row r="164">
@@ -11546,7 +11554,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1075963-12366-CM26</t>
+          <t>1075963-12314-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11586,12 +11594,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11601,13 +11609,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1409.12</v>
+        <v>5417.38</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1075963-12314-CM26</t>
+          <t>1075963-12366-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11627,7 +11635,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11647,12 +11655,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11662,7 +11670,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5417.38</v>
+        <v>1409.12</v>
       </c>
     </row>
     <row r="180">
@@ -11688,7 +11696,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11728,6 +11736,1079 @@
       </c>
       <c r="M180" s="2" t="n">
         <v>1516.25</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>3348-117-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>2163.89</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2366-544-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>MADEGOM S.A.</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>84.609.600-0</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>11042.55</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2366-520-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>3757.1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2366-525-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>MEDIPLEX S A</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>86.383.300-0</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>2276.9</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2366-527-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>2800.46</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2366-537-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>9280.209999999999</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2366-539-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>ISI-MED SPA</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>77.430.568-8</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>948.74</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2366-541-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>12994.59</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1110404-978-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>1291.7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1347870-157-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>77.910.467-2</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>31213.91</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1075963-12923-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>BLUEMEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>17257.64</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1075963-13597-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>2101.06</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1075963-13239-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>861.5700000000001</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1075963-13702-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>765.64</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>5951-138-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1075963-13756-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>4013.04</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1075963-13793-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>1529.13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -11058,7 +11058,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/arica-y-parinacota.xlsx
@@ -11822,7 +11822,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
